--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.95976532020687</v>
+        <v>12.18096186453362</v>
       </c>
       <c r="D2" t="n">
-        <v>63.28493317114188</v>
+        <v>10.28380164031056</v>
       </c>
       <c r="E2" t="n">
-        <v>17.89628614908981</v>
+        <v>2.908146499227093</v>
       </c>
       <c r="F2" t="n">
-        <v>18.21928821706098</v>
+        <v>2.960634335272409</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.01642533127931</v>
+        <v>11.37766911633289</v>
       </c>
       <c r="D3" t="n">
-        <v>58.74857347097181</v>
+        <v>9.54664318903292</v>
       </c>
       <c r="E3" t="n">
-        <v>17.89628614908981</v>
+        <v>2.908146499227093</v>
       </c>
       <c r="F3" t="n">
-        <v>18.21928821706098</v>
+        <v>2.960634335272409</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.87400957226047</v>
+        <v>8.592026555492327</v>
       </c>
       <c r="D4" t="n">
-        <v>41.65852210107565</v>
+        <v>6.769509841424794</v>
       </c>
       <c r="E4" t="n">
-        <v>17.89628614908981</v>
+        <v>2.908146499227093</v>
       </c>
       <c r="F4" t="n">
-        <v>18.21928821706098</v>
+        <v>2.960634335272409</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.97608796401472</v>
+        <v>8.608614294152392</v>
       </c>
       <c r="D5" t="n">
-        <v>42.83692402011722</v>
+        <v>6.961000153269048</v>
       </c>
       <c r="E5" t="n">
-        <v>17.89628614908981</v>
+        <v>2.908146499227093</v>
       </c>
       <c r="F5" t="n">
-        <v>18.21928821706098</v>
+        <v>2.960634335272409</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.20137163878212</v>
+        <v>6.045222891302095</v>
       </c>
       <c r="D6" t="n">
-        <v>31.06220734843788</v>
+        <v>5.047608694121156</v>
       </c>
       <c r="E6" t="n">
-        <v>17.89628614908981</v>
+        <v>2.908146499227093</v>
       </c>
       <c r="F6" t="n">
-        <v>18.21928821706098</v>
+        <v>2.960634335272409</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.950287570235043</v>
+        <v>1.616921730163194</v>
       </c>
       <c r="D7" t="n">
-        <v>5.625736402677679</v>
+        <v>0.914182165435123</v>
       </c>
       <c r="E7" t="n">
-        <v>17.89628614908981</v>
+        <v>2.908146499227093</v>
       </c>
       <c r="F7" t="n">
-        <v>18.21928821706098</v>
+        <v>2.960634335272409</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.14503378072045</v>
+        <v>9.936067989367073</v>
       </c>
       <c r="D8" t="n">
-        <v>23.63825720993033</v>
+        <v>3.841216796613679</v>
       </c>
       <c r="E8" t="n">
-        <v>17.89628614908981</v>
+        <v>2.908146499227093</v>
       </c>
       <c r="F8" t="n">
-        <v>18.21928821706098</v>
+        <v>2.960634335272409</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.99365547670759</v>
+        <v>9.911469014964982</v>
       </c>
       <c r="D9" t="n">
-        <v>27.10210366658128</v>
+        <v>4.404091845819458</v>
       </c>
       <c r="E9" t="n">
-        <v>17.89628614908981</v>
+        <v>2.908146499227093</v>
       </c>
       <c r="F9" t="n">
-        <v>18.21928821706098</v>
+        <v>2.960634335272409</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>58.693353598683</v>
+        <v>9.537669959785989</v>
       </c>
       <c r="D10" t="n">
-        <v>8.627946476794477</v>
+        <v>1.402041302479103</v>
       </c>
       <c r="E10" t="n">
-        <v>17.89628614908981</v>
+        <v>2.908146499227093</v>
       </c>
       <c r="F10" t="n">
-        <v>18.21928821706098</v>
+        <v>2.960634335272409</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.62828831236471</v>
+        <v>6.439596850759266</v>
       </c>
       <c r="D11" t="n">
-        <v>23.00300132220994</v>
+        <v>3.737987714859115</v>
       </c>
       <c r="E11" t="n">
-        <v>17.89628614908981</v>
+        <v>2.908146499227093</v>
       </c>
       <c r="F11" t="n">
-        <v>18.21928821706098</v>
+        <v>2.960634335272409</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
